--- a/data/Escenarios_DCH_costos_nuevos/Costo_variable/Swap_variable_3estaciones_530kW/elmo_data.xlsx
+++ b/data/Escenarios_DCH_costos_nuevos/Costo_variable/Swap_variable_3estaciones_530kW/elmo_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH_costos_nuevos\Costo_variable\Swap_variable_3estaciones_530kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A52FED-E9F3-4AC1-A5EC-126F93992044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4CA141-FE8F-4440-97D6-44349B4D6474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="396">
   <si>
     <t>id</t>
   </si>
@@ -1153,12 +1153,6 @@
   </si>
   <si>
     <t>station_name</t>
-  </si>
-  <si>
-    <t>distance_to_dn</t>
-  </si>
-  <si>
-    <t>man_time</t>
   </si>
   <si>
     <t>USD</t>
@@ -2229,7 +2223,7 @@
         <v>62</v>
       </c>
       <c r="AE1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2321,10 +2315,10 @@
         <v>37</v>
       </c>
       <c r="AD2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AE2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2335,10 +2329,10 @@
         <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>52</v>
@@ -2430,10 +2424,10 @@
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E4" s="21" t="s">
         <v>52</v>
@@ -2525,10 +2519,10 @@
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>52</v>
@@ -2620,10 +2614,10 @@
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E6" s="21" t="s">
         <v>52</v>
@@ -2716,10 +2710,10 @@
         <v>351</v>
       </c>
       <c r="C7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E7" s="21" t="s">
         <v>52</v>
@@ -2812,10 +2806,10 @@
         <v>352</v>
       </c>
       <c r="C8" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E8" s="21" t="s">
         <v>52</v>
@@ -2908,10 +2902,10 @@
         <v>353</v>
       </c>
       <c r="C9" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>52</v>
@@ -3004,10 +2998,10 @@
         <v>354</v>
       </c>
       <c r="C10" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E10" s="21" t="s">
         <v>52</v>
@@ -3100,10 +3094,10 @@
         <v>355</v>
       </c>
       <c r="C11" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E11" s="21" t="s">
         <v>52</v>
@@ -3196,10 +3190,10 @@
         <v>356</v>
       </c>
       <c r="C12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E12" s="21" t="s">
         <v>52</v>
@@ -3292,10 +3286,10 @@
         <v>357</v>
       </c>
       <c r="C13" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E13" s="21" t="s">
         <v>52</v>
@@ -3388,10 +3382,10 @@
         <v>358</v>
       </c>
       <c r="C14" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E14" s="21" t="s">
         <v>52</v>
@@ -3487,7 +3481,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC93900-5A86-4519-AB89-460E8AC441EE}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
@@ -3500,7 +3494,7 @@
     <col min="10" max="10" width="22.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3508,40 +3502,34 @@
         <v>371</v>
       </c>
       <c r="C1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F1" t="s">
         <v>389</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>390</v>
       </c>
-      <c r="E1" t="s">
-        <v>397</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>391</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J1" t="s">
         <v>392</v>
       </c>
-      <c r="H1" t="s">
-        <v>393</v>
-      </c>
-      <c r="I1" t="s">
-        <v>395</v>
-      </c>
-      <c r="J1" t="s">
-        <v>394</v>
-      </c>
       <c r="K1" t="s">
-        <v>372</v>
-      </c>
-      <c r="L1" t="s">
-        <v>373</v>
-      </c>
-      <c r="M1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3549,19 +3537,19 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H2" t="s">
         <v>51</v>
@@ -3573,21 +3561,15 @@
         <v>51</v>
       </c>
       <c r="K2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" t="s">
-        <v>375</v>
-      </c>
-      <c r="M2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C3">
         <v>35722</v>
@@ -3614,21 +3596,15 @@
         <v>2</v>
       </c>
       <c r="K3">
-        <v>168</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
         <v>1500</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C4">
         <v>35722</v>
@@ -3655,21 +3631,15 @@
         <v>2</v>
       </c>
       <c r="K4">
-        <v>168</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
         <v>1500</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C5">
         <v>35722</v>
@@ -3696,12 +3666,6 @@
         <v>2</v>
       </c>
       <c r="K5">
-        <v>253</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
         <v>1500</v>
       </c>
     </row>
@@ -3721,22 +3685,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D1" t="s">
         <v>377</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>378</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>379</v>
       </c>
-      <c r="E1" t="s">
-        <v>380</v>
-      </c>
-      <c r="F1" t="s">
-        <v>381</v>
-      </c>
       <c r="G1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H1" s="13" t="s">
         <v>53</v>
@@ -3750,7 +3714,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
@@ -3762,7 +3726,7 @@
         <v>34</v>
       </c>
       <c r="G2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H2" s="33" t="s">
         <v>4</v>
@@ -3773,7 +3737,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C3">
         <v>69682</v>
@@ -3791,7 +3755,7 @@
         <v>79000</v>
       </c>
       <c r="H3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
